--- a/bank_soal_updated.xlsx
+++ b/bank_soal_updated.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CAT\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7153DBA7-C72E-4022-8CA5-519B76EAAE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="110">
   <si>
     <t>No</t>
   </si>
@@ -202,13 +208,399 @@
   </si>
   <si>
     <t>Sinyal pembatalan/selesai keadaan darurat (All Clear) ditandai dengan 1 tiupan pendek diikuti 1 tiupan panjang suling/alarm selama ±10 detik.</t>
+  </si>
+  <si>
+    <t>What are the signals if someone falls into the sea?</t>
+  </si>
+  <si>
+    <t>1 short blast followed by 1 long blast with a flute or continuous alarm for a period of
+±10 seconds</t>
+  </si>
+  <si>
+    <t>3 short blasts on the ship's flute and 3 short blasts on the general alarm</t>
+  </si>
+  <si>
+    <t>What are the signals for abandoning the ship?</t>
+  </si>
+  <si>
+    <t>When a ship experiences a fire condition, what signal is sounded?</t>
+  </si>
+  <si>
+    <t>Below are the dangers of closed spaces on ships, among others?</t>
+  </si>
+  <si>
+    <t>Low oxygen levels</t>
+  </si>
+  <si>
+    <t>All answers are correct</t>
+  </si>
+  <si>
+    <t>The presence of dangerous and toxic gases</t>
+  </si>
+  <si>
+    <t>Slippery and Dark</t>
+  </si>
+  <si>
+    <t>Which of the following is the most appropriate statement for the "Ship Security Plan"?</t>
+  </si>
+  <si>
+    <t>a plan developed to ensure the application of measures on board the ship designed to
+protect persons on board, cargo, cargo transport units, ship’s stores or the ship from
+the risks of a safety incident</t>
+  </si>
+  <si>
+    <t>a plan developed to ensure the application of measures on board the ship designed to
+protect persons on board, cargo, cargo transport units, ship’s stores or the ship from
+the risks of a security incident</t>
+  </si>
+  <si>
+    <t>a plan developed to change the application of measures on board the ship designed
+to protect persons on board, cargo, cargo transport units, ship’s stores or the ship
+from the risks of a security incident</t>
+  </si>
+  <si>
+    <t>a plan developed to ensure the application of measures designed to protect the port
+facility and ships, persons, cargo, cargo transport units and ships stores within the
+port facility from the risks of a security incident</t>
+  </si>
+  <si>
+    <t>The person on board the ship, accountable to the master, designated by the company as responsible for the
+security of the ship, including implementation and maintenance of the ship security plan and for liaison with
+the company security officer and port facility security officers is…..</t>
+  </si>
+  <si>
+    <t>Ship security officer</t>
+  </si>
+  <si>
+    <t>Company security officer</t>
+  </si>
+  <si>
+    <t>Port security officer</t>
+  </si>
+  <si>
+    <t>Chief security officer</t>
+  </si>
+  <si>
+    <t>What does MRCC sand for?</t>
+  </si>
+  <si>
+    <t>Maritime Rescue Coordination Course</t>
+  </si>
+  <si>
+    <t>Maritime Radio Coordination Centre</t>
+  </si>
+  <si>
+    <t>Maritime Rescue Coordination Centre.</t>
+  </si>
+  <si>
+    <t>Marine Rescue Coordination Centre</t>
+  </si>
+  <si>
+    <t>Is the vessel sea worthy?</t>
+  </si>
+  <si>
+    <t>No the vessel is not seaworthy, the vessel will not be repaired and re-inspected</t>
+  </si>
+  <si>
+    <t>No, the vessel is not seaworthy, the vessel must be repaired and re-inspected</t>
+  </si>
+  <si>
+    <t>No, the vessel is not seaworthy, the vessel must not be repaired and re-inspirated</t>
+  </si>
+  <si>
+    <t>None of the above</t>
+  </si>
+  <si>
+    <t>If someone falls overboard the immediate action should……</t>
+  </si>
+  <si>
+    <t>immediately throw the nearest lifebuoy overboard.</t>
+  </si>
+  <si>
+    <t>Immediately throw the nearest extinguisher overboard</t>
+  </si>
+  <si>
+    <t>immediately throw the nearest light overboard</t>
+  </si>
+  <si>
+    <t>immediately throw the nearest anchor overboard</t>
+  </si>
+  <si>
+    <t>What does the abbreviation ISPS mean</t>
+  </si>
+  <si>
+    <t>International Code for the Security of Ships and Port Function</t>
+  </si>
+  <si>
+    <t>International Code for the Safety and Security on the Port</t>
+  </si>
+  <si>
+    <t>International Code for the Security of Ships and Port Face</t>
+  </si>
+  <si>
+    <t>International Code for the Security of Ships and Port Facilities</t>
+  </si>
+  <si>
+    <t>Sinyal Orang Jatuh ke Laut (Man Overboard / MOB) ditandai dengan 3 tiupan pendek/panjang pada suling kapal dan alarm umum secara berulang untuk memberi peringatan ke seluruh awak kapal.</t>
+  </si>
+  <si>
+    <t>Sinyal Meninggalkan Kapal (Abandon Ship) menggunakan sinyal alarm umum yaitu 7 tiupan pendek diikuti 1 tiupan panjang suling/alarm kapal secara terus menerus, didampingi perintah lisan Nahkoda.</t>
+  </si>
+  <si>
+    <r>
+      <t>Sinyal Keadaan Darurat Kebakaran (Fire Alarm) ditandai dengan bunyi suling/alarm kapal secara terus-menerus (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>continuous alarm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) atau pola khusus sesuai </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Muster List</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kapal.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bahaya utama memasuki ruang tertutup (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>enclosed space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) meliputi kadar oksigen rendah (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>deplesi oksigen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>), adanya gas beracun/mudah terbakar, serta kondisi fisik area yang gelap dan licin.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ship Security Plan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (SSP) sesuai Kode ISPS Bagian A/2.1.10 adalah rencana tertulis untuk memastikan tindakan perlindungan terhadap personil, muatan, dan kapal dari risiko insiden keamanan (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>security incident</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ship Security Officer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (SSO) adalah perwira di atas kapal yang ditunjuk perusahaan dan bertanggung jawab kepada Nahkoda atas pelaksanaan SSP serta jalur komunikasi ke CSO dan PFSO.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MRCC adalah singkatan dari </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Maritime Rescue Coordination Centre</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, yaitu pusat organisasi dan koordinasi operasi pencarian serta pertolongan (SAR) di wilayah maritim.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Jika kapal dinyatakan tidak laik laut (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>not seaworthy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>), kapal dilarang berlayar dan wajib menjalani perbaikan serta inspeksi ulang hingga memenuhi kualifikasi keselamatan.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tindakan langsung dan pertama saat mengetahui ada orang jatuh ke laut (MOB) adalah melemparkan pelampung penolong (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lifebuoy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) terdekat untuk bantuan apung dan penanda lokasi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ISPS Code adalah singkatan dari </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>International Ship and Port Facility Security Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, yaitu amandemen SOLAS 1974 Bab XI-2 mengenai standar keamanan kapal dan fasilitas pelabuhan.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,6 +610,19 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="DejaVuSansCondensed"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -260,24 +665,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -315,7 +730,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -349,6 +764,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -383,9 +799,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -558,9 +975,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
@@ -914,6 +1331,326 @@
         <v>59</v>
       </c>
     </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
